--- a/報酬計算表.xlsx
+++ b/報酬計算表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\趣味\中川　自宅用\シナリオ集用オリジナルシステム\o-systmeファンタジー\ヴァルドリア大陸ガイド\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91FAC55-E400-4365-BCC5-55DDB857967C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC913AC8-F2D4-4EB5-A262-AE15DCB44946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="180" windowWidth="13725" windowHeight="14460" xr2:uid="{819365C5-BFDD-462D-A454-26234D9AFE06}"/>
+    <workbookView xWindow="405" yWindow="150" windowWidth="14715" windowHeight="14280" xr2:uid="{819365C5-BFDD-462D-A454-26234D9AFE06}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -367,7 +367,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -392,10 +392,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
@@ -812,11 +809,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="6">
-        <f>F3 + G3 + H3</f>
         <v>0</v>
       </c>
       <c r="J3" s="6">
-        <f>1</f>
+        <f>1+(F3*0.05)+(G3*0.1)+(H3*0.2)+IF(I3&lt;=2,0,IF(I3&lt;=4,0.05,IF(I3&lt;=6,0.1,0.2)))</f>
         <v>1</v>
       </c>
       <c r="K3" s="7">
@@ -837,7 +833,7 @@
       <c r="J4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="9" t="s">
         <v>26</v>
       </c>
     </row>
@@ -852,11 +848,11 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="3">
-        <v>1</v>
-      </c>
-      <c r="K5" s="7">
-        <f>IF(J5=0,"",K3/J5)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K5" s="7" t="str">
+        <f>IF(J5=0,"",CEILING(K3/J5,1))</f>
+        <v/>
       </c>
     </row>
     <row r="6" spans="1:11" ht="20.25" thickTop="1" x14ac:dyDescent="0.4">
@@ -1143,16 +1139,6 @@
     </row>
     <row r="24" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/報酬計算表.xlsx
+++ b/報酬計算表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\趣味\中川　自宅用\シナリオ集用オリジナルシステム\o-systmeファンタジー\ヴァルドリア大陸ガイド\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC913AC8-F2D4-4EB5-A262-AE15DCB44946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68EE3D7-F77D-4E37-B22F-73815ED25DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="150" windowWidth="14715" windowHeight="14280" xr2:uid="{819365C5-BFDD-462D-A454-26234D9AFE06}"/>
+    <workbookView xWindow="585" yWindow="480" windowWidth="17265" windowHeight="14280" xr2:uid="{819365C5-BFDD-462D-A454-26234D9AFE06}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>特技総数</t>
     <rPh sb="0" eb="2">
@@ -96,13 +96,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>最終報酬額</t>
-    <rPh sb="0" eb="5">
-      <t>サイシュウホウシュウガク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>報酬決定表</t>
     <rPh sb="0" eb="5">
       <t>ホウシュウケッテイヒョウ</t>
@@ -203,8 +196,25 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>パーティ人数</t>
-    <rPh sb="4" eb="6">
+    <t>最終受取額</t>
+    <rPh sb="0" eb="5">
+      <t>サイシュウウケトリガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>報酬総額</t>
+    <rPh sb="0" eb="2">
+      <t>ホウシュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パーティー人数</t>
+    <rPh sb="5" eb="7">
       <t>ニンズウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -216,6 +226,13 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>ホウシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ギルド手数料</t>
+    <rPh sb="3" eb="6">
+      <t>テスウリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -367,7 +384,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -397,6 +414,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -732,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04F3C2CE-9361-4F77-BB49-5768735CBEB3}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.75" customWidth="1"/>
@@ -741,14 +764,16 @@
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="17.125" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="29.25" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="29.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="20.25" thickTop="1" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="20.25" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -757,10 +782,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>4</v>
@@ -778,22 +803,24 @@
         <v>1</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="L2" s="10"/>
+      <c r="M2" s="11"/>
+    </row>
+    <row r="3" spans="1:13" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="6">
         <f>_xlfn.XLOOKUP(B3,$A$10:$A$15,$B$10:$B$15)</f>
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="6">
         <f>_xlfn.XLOOKUP(D3, $E$10:$E$15, $F$10:$F$15)</f>
@@ -809,18 +836,25 @@
         <v>0</v>
       </c>
       <c r="I3" s="6">
+        <f>F3+G3+H3</f>
         <v>0</v>
       </c>
       <c r="J3" s="6">
-        <f>1+(F3*0.05)+(G3*0.1)+(H3*0.2)+IF(I3&lt;=2,0,IF(I3&lt;=4,0.05,IF(I3&lt;=6,0.1,0.2)))</f>
+        <f>1
+ + (F3*0.05)
+ + (G3*0.1)
+ + (H3*0.2)
+ + IF(I3&lt;=2,0, IF(I3&lt;=4,0.05, IF(I3&lt;=6,0.1, 0.2)))</f>
         <v>1</v>
       </c>
       <c r="K3" s="7">
         <f>C3 * J3 * E3</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="20.25" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+    </row>
+    <row r="4" spans="1:13" ht="20.25" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -831,13 +865,14 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="K4" s="9">
+        <f>K3 * IF(B3="A",0.2, IF(OR(B3="B",B3="C"),0.15, 0.1))</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -847,15 +882,15 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="3">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7" t="str">
-        <f>IF(J5=0,"",CEILING(K3/J5,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="20.25" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="7">
+        <f>K3 - K4</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="20.25" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -865,10 +900,14 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-    </row>
-    <row r="7" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="J6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -878,10 +917,15 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-    </row>
-    <row r="8" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7" t="str">
+        <f>IF(J7=0,"",ROUND(K5/J7,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="20.25" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -894,7 +938,7 @@
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -907,9 +951,9 @@
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
     </row>
-    <row r="10" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="8">
         <v>1</v>
@@ -917,7 +961,7 @@
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" s="8">
         <v>1</v>
@@ -928,9 +972,9 @@
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="8">
         <v>3</v>
@@ -938,7 +982,7 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" s="8">
         <v>2</v>
@@ -949,9 +993,9 @@
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
     </row>
-    <row r="12" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="8">
         <v>7</v>
@@ -959,7 +1003,7 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12" s="8">
         <v>3</v>
@@ -970,9 +1014,9 @@
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
     </row>
-    <row r="13" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="8">
         <v>16</v>
@@ -980,7 +1024,7 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" s="8">
         <v>3</v>
@@ -991,9 +1035,9 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="14" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="8">
         <v>31</v>
@@ -1001,7 +1045,7 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" s="8">
         <v>4</v>
@@ -1012,9 +1056,9 @@
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="8">
         <v>80</v>
@@ -1022,7 +1066,7 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="8">
         <v>5</v>
@@ -1033,7 +1077,7 @@
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
     </row>
-    <row r="16" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
